--- a/backend/data/financials_by_company/000560.SZ.xlsx
+++ b/backend/data/financials_by_company/000560.SZ.xlsx
@@ -4085,192 +4085,192 @@
       </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="ET1" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Building 8, No. 8 Courtyard</t>
+          <t>Building 7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beichen East Road Chaoyang District</t>
+          <t>No. 8 Beichen East Road Chaoyang District</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>5i5j Holding Group Co., Ltd. provides real estate brokerage services in China and internationally. It provides also offers housing asset management, commercial asset management, and post-house derivative services. The company offers digital smart products, such as online real estate dictionary, VR viewing, smart recommendation, IM tools, broker operation platform, online signing, smart customer service, and other digital smart products. In addition, it is involved in the second-hand housing brokerage business includes buying and selling brokerage and leasing brokerage services. Further, the company provides housing asset management services under the Xiangyu brand. The company was formerly known as Kunming Sinobright (Group) Co., Ltd. and changed its name to 5i5j Holding Group Co., Ltd. in April 2018. 5i5j Holding Group Co., Ltd. was founded in 1959 and is headquartered in Beijing, China.</t>
+          <t>5i5j Holding Group Co., Ltd. provides real estate brokerage services in China and internationally. It provides brokerage business, such as buying, selling, and leasing of existing homes; property registration, verification, display, and inquiry, as well as professional consultation and matching transaction; and online services for verification, signing, fulfillment, and customer support services. The company also offers asset management business, including housing rental management business; new home sales; commercial leasing and services, comprising commercial leasing and services; and asset management services. In addition, it provides, an internet-based residential living service platform with residential transaction services at its core, focusing on providing digital industry solutions and integrated operational services. The company was formerly known as Kunming Sinobright (Group) Co., Ltd. and changed its name to 5i5j Holding Group Co., Ltd. in April 2018. 5i5j Holding Group Co., Ltd. was founded in 1959 and is headquartered in Beijing, China.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4370,28 +4370,28 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="U2" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="X2" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -4409,31 +4409,31 @@
         <v>0.88</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.622</v>
+        <v>0.649</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19.272726</v>
       </c>
       <c r="AI2" t="n">
-        <v>74364587</v>
+        <v>57503671</v>
       </c>
       <c r="AJ2" t="n">
-        <v>74364587</v>
+        <v>57503671</v>
       </c>
       <c r="AK2" t="n">
-        <v>94201039</v>
+        <v>89419219</v>
       </c>
       <c r="AL2" t="n">
-        <v>68175301</v>
+        <v>73707963</v>
       </c>
       <c r="AM2" t="n">
-        <v>68175301</v>
+        <v>73707963</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -4442,13 +4442,13 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>5182102016</v>
+        <v>4993661440</v>
       </c>
       <c r="AS2" t="n">
-        <v>5182101872</v>
+        <v>5040771821</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AU2" t="n">
         <v>3.65</v>
@@ -4460,13 +4460,13 @@
         <v>0.470676</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.52782995</v>
+        <v>0.5086360599999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.8222</v>
+        <v>2.6706</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.00765</v>
+        <v>2.9627</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>11945517056</v>
+        <v>11757076480</v>
       </c>
       <c r="BF2" t="n">
         <v>-0.00993</v>
@@ -4495,10 +4495,10 @@
         <v>2355500851</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.22288999</v>
+        <v>0.23398</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.15833001</v>
+        <v>0.17719</v>
       </c>
       <c r="BK2" t="n">
         <v>2355500851</v>
@@ -4507,7 +4507,7 @@
         <v>3.94</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5583756600000001</v>
+        <v>0.5380710399999999</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4539,16 +4539,16 @@
         <v>1530057600</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.217</v>
+        <v>1.198</v>
       </c>
       <c r="BX2" t="n">
-        <v>-18.367</v>
+        <v>-18.077</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.24398625</v>
+        <v>-0.28474575</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CA2" t="n">
         <v>0.0043</v>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="CE2" t="n">
         <v>1</v>
@@ -4667,145 +4667,145 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DH2" t="n">
-        <v>-0.26853186</v>
-      </c>
-      <c r="DI2" t="n">
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>finmb_12726148</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>760152600000</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.00999999</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>2.08 - 2.15</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>89419219</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.109999895</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.054726318</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>2.01 - 3.65</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>-1.5300002</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.41917813</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-28.474575</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1651229940</v>
+      </c>
+      <c r="EB2" t="n">
         <v>1651492800</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="EC2" t="n">
         <v>-0.04</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="ED2" t="n">
         <v>0.11</v>
       </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>2.1 - 2.21</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>94201039</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.10000014</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.04761912</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>2.1 - 3.65</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.39726028</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-24.398624</v>
-      </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EE2" t="n">
+        <v>-0.55060005</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.20617092</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.8427</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.2844365</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EK2" t="inlineStr">
         <is>
           <t>1.0 - Strong Buy</t>
         </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.6222</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.2204663</v>
-      </c>
-      <c r="EA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>760152600000</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>1782111888</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>finmb_12726148</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
       </c>
       <c r="EL2" t="b">
         <v>0</v>
       </c>
-      <c r="EM2" t="n">
-        <v>1651229940</v>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="EN2" t="n">
-        <v>-0.80764985</v>
+        <v>1783062294</v>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>5I5J HOLDING GROUP CO LTD</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>5I5J HOLDING GROUP CO LTD</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
           <t>5i5j Holding Group Co., Ltd.</t>
         </is>
       </c>
+      <c r="EQ2" t="n">
+        <v>0.4739332</v>
+      </c>
       <c r="ER2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>15</v>
+        <v>2.12</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="ET2" t="inlineStr"/>
     </row>
